--- a/results_tables.xlsx
+++ b/results_tables.xlsx
@@ -483,16 +483,16 @@
         </is>
       </c>
       <c r="D4">
-        <v>1.081</v>
+        <v>1.201</v>
       </c>
       <c r="E4">
-        <v>0.763</v>
+        <v>0.917</v>
       </c>
       <c r="F4">
-        <v>1.532</v>
+        <v>1.572</v>
       </c>
       <c r="G4">
-        <v>0.661</v>
+        <v>0.184</v>
       </c>
     </row>
     <row r="5">
@@ -570,16 +570,16 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.956</v>
+        <v>0.915</v>
       </c>
       <c r="E7">
-        <v>0.841</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="F7">
-        <v>1.088</v>
+        <v>1.025</v>
       </c>
       <c r="G7">
-        <v>0.498</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="8">
@@ -657,16 +657,16 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.967</v>
+        <v>0.952</v>
       </c>
       <c r="E10">
-        <v>0.829</v>
+        <v>0.849</v>
       </c>
       <c r="F10">
-        <v>1.128</v>
+        <v>1.068</v>
       </c>
       <c r="G10">
-        <v>0.667</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="11">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="D13">
-        <v>1.08869647462976</v>
+        <v>1.00490612547212</v>
       </c>
       <c r="E13">
-        <v>0.8835505268666682</v>
+        <v>0.8528984946638464</v>
       </c>
       <c r="F13">
-        <v>1.341473948382501</v>
+        <v>1.184005280029714</v>
       </c>
       <c r="G13">
-        <v>0.4250089304493059</v>
+        <v>0.9533601948572693</v>
       </c>
       <c r="H13">
-        <v>0.1065244312116344</v>
+        <v>0.08367799299926831</v>
       </c>
       <c r="I13">
-        <v>0.7977614598503469</v>
+        <v>0.05848765586314938</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="D16">
-        <v>1.064</v>
+        <v>1.158</v>
       </c>
       <c r="E16">
-        <v>0.702</v>
+        <v>0.828</v>
       </c>
       <c r="F16">
-        <v>1.614</v>
+        <v>1.619</v>
       </c>
       <c r="G16">
-        <v>0.77</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="17">
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="D19">
-        <v>-0.5590000000000001</v>
+        <v>-0.397</v>
       </c>
       <c r="E19">
-        <v>-1.768</v>
+        <v>-1.409</v>
       </c>
       <c r="F19">
-        <v>0.65</v>
+        <v>0.616</v>
       </c>
       <c r="G19">
-        <v>0.365</v>
+        <v>0.443</v>
       </c>
     </row>
     <row r="20">
@@ -1038,16 +1038,16 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.144</v>
+        <v>0.083</v>
       </c>
       <c r="E22">
-        <v>-0.294</v>
+        <v>-0.273</v>
       </c>
       <c r="F22">
-        <v>0.583</v>
+        <v>0.44</v>
       </c>
       <c r="G22">
-        <v>0.519</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="23">
@@ -1125,16 +1125,16 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.185</v>
+        <v>0.098</v>
       </c>
       <c r="E25">
-        <v>-0.32</v>
+        <v>-0.327</v>
       </c>
       <c r="F25">
-        <v>0.6899999999999999</v>
+        <v>0.524</v>
       </c>
       <c r="G25">
-        <v>0.472</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="26">
@@ -1234,22 +1234,22 @@
         </is>
       </c>
       <c r="D28">
-        <v>-0.6581362787311189</v>
+        <v>-0.5449925990258451</v>
       </c>
       <c r="E28">
-        <v>-1.418283644467062</v>
+        <v>-1.152511258232092</v>
       </c>
       <c r="F28">
-        <v>0.1020110870048243</v>
+        <v>0.06252606018040174</v>
       </c>
       <c r="G28">
-        <v>0.09025312147461216</v>
+        <v>0.07913566553542921</v>
       </c>
       <c r="H28">
-        <v>0.3878302886407873</v>
+        <v>0.3099584995950239</v>
       </c>
       <c r="I28">
-        <v>-1.696969777780023</v>
+        <v>-1.758276026429038</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1332,16 +1332,16 @@
         </is>
       </c>
       <c r="D31">
-        <v>0.87</v>
+        <v>0.478</v>
       </c>
       <c r="E31">
-        <v>-0.646</v>
+        <v>-0.718</v>
       </c>
       <c r="F31">
-        <v>2.386</v>
+        <v>1.673</v>
       </c>
       <c r="G31">
-        <v>0.261</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="32">
@@ -1419,16 +1419,16 @@
         </is>
       </c>
       <c r="D34">
-        <v>-0.9419999999999999</v>
+        <v>-0.612</v>
       </c>
       <c r="E34">
-        <v>-4.394</v>
+        <v>-1.38</v>
       </c>
       <c r="F34">
-        <v>2.509</v>
+        <v>0.155</v>
       </c>
       <c r="G34">
-        <v>0.602</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="35">
@@ -1506,16 +1506,16 @@
         </is>
       </c>
       <c r="D37">
-        <v>0.311</v>
+        <v>0.157</v>
       </c>
       <c r="E37">
-        <v>-0.462</v>
+        <v>-0.062</v>
       </c>
       <c r="F37">
-        <v>1.083</v>
+        <v>0.377</v>
       </c>
       <c r="G37">
-        <v>0.446</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="38">
@@ -1593,16 +1593,16 @@
         </is>
       </c>
       <c r="D40">
-        <v>0.479</v>
+        <v>0.17</v>
       </c>
       <c r="E40">
-        <v>-0.644</v>
+        <v>-0.093</v>
       </c>
       <c r="F40">
-        <v>1.603</v>
+        <v>0.433</v>
       </c>
       <c r="G40">
-        <v>0.419</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="41">
@@ -1702,22 +1702,22 @@
         </is>
       </c>
       <c r="D43">
-        <v>0.3834108580912701</v>
+        <v>0.1351478055817372</v>
       </c>
       <c r="E43">
-        <v>-1.46827855710829</v>
+        <v>-0.3871481476442171</v>
       </c>
       <c r="F43">
-        <v>2.23510027329083</v>
+        <v>0.6574437588076913</v>
       </c>
       <c r="G43">
-        <v>0.6920050186455344</v>
+        <v>0.6136338333666915</v>
       </c>
       <c r="H43">
-        <v>0.944739497550796</v>
+        <v>0.2664775271560991</v>
       </c>
       <c r="I43">
-        <v>0.4058376505748402</v>
+        <v>0.5071639887387926</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -1800,16 +1800,16 @@
         </is>
       </c>
       <c r="D46">
-        <v>-1.358</v>
+        <v>-0.638</v>
       </c>
       <c r="E46">
-        <v>-4.687</v>
+        <v>-1.497</v>
       </c>
       <c r="F46">
-        <v>1.971</v>
+        <v>0.222</v>
       </c>
       <c r="G46">
-        <v>0.439</v>
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
@@ -1856,16 +1856,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>2.434</v>
+        <v>2.125</v>
       </c>
       <c r="C2">
-        <v>-1.113</v>
+        <v>-0.63</v>
       </c>
       <c r="D2">
-        <v>5.98</v>
+        <v>4.881</v>
       </c>
       <c r="E2">
-        <v>0.179</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="3">
@@ -1875,16 +1875,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>-3.65</v>
+        <v>-3.247</v>
       </c>
       <c r="C3">
-        <v>-8.196</v>
+        <v>-7.068</v>
       </c>
       <c r="D3">
-        <v>0.896</v>
+        <v>0.573</v>
       </c>
       <c r="E3">
-        <v>0.116</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="4">
@@ -1894,16 +1894,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>-4.17</v>
+        <v>-3.5</v>
       </c>
       <c r="C4">
-        <v>-7.921</v>
+        <v>-6.463</v>
       </c>
       <c r="D4">
-        <v>-0.42</v>
+        <v>-0.537</v>
       </c>
       <c r="E4">
-        <v>0.03</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="5">
@@ -1913,16 +1913,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>-3.02</v>
+        <v>-2.448</v>
       </c>
       <c r="C5">
-        <v>-6.664</v>
+        <v>-5.312</v>
       </c>
       <c r="D5">
-        <v>0.623</v>
+        <v>0.416</v>
       </c>
       <c r="E5">
-        <v>0.105</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="6">
@@ -1932,16 +1932,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>-1.854</v>
+        <v>-2.251</v>
       </c>
       <c r="C6">
-        <v>-5.696</v>
+        <v>-5.314</v>
       </c>
       <c r="D6">
-        <v>1.988</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="E6">
-        <v>0.345</v>
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
